--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -44,6 +44,18 @@
     <t>SelectParam</t>
   </si>
   <si>
+    <t>HitAction</t>
+  </si>
+  <si>
+    <t>HitActionTimes</t>
+  </si>
+  <si>
+    <t>SelfHitAction</t>
+  </si>
+  <si>
+    <t>SelfHitActionTimes</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -53,6 +65,12 @@
     <t>(list#sep=,),string</t>
   </si>
   <si>
+    <t>(list#spe=,),int</t>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -63,6 +81,18 @@
   </si>
   <si>
     <t>目标选择参数</t>
+  </si>
+  <si>
+    <t>命中行为</t>
+  </si>
+  <si>
+    <t>技能命中时间点</t>
+  </si>
+  <si>
+    <t>命中自身行为</t>
+  </si>
+  <si>
+    <t>技能命中自身时间点</t>
   </si>
 </sst>
 </file>
@@ -1021,18 +1051,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.875" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="5" max="6" width="26.875" style="2" customWidth="1"/>
+    <col min="7" max="8" width="23.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="29.375" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1048,59 +1080,80 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:5">
+    <row r="2" s="1" customFormat="1" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:5">
+    <row r="3" s="1" customFormat="1" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="2:2">
       <c r="B4" s="3">
         <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="3">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -56,21 +56,33 @@
     <t>SelfHitActionTimes</t>
   </si>
   <si>
+    <t>Buffs</t>
+  </si>
+  <si>
+    <t>StartEffect</t>
+  </si>
+  <si>
+    <t>HitEffect</t>
+  </si>
+  <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
+    <t>HitAnimation</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>(list#sep=,),string</t>
+    <t>(list#sep=,),int</t>
   </si>
   <si>
     <t>(list#spe=,),int</t>
   </si>
   <si>
-    <t>(list#sep=,),int</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -93,6 +105,24 @@
   </si>
   <si>
     <t>技能命中自身时间点</t>
+  </si>
+  <si>
+    <t>命中Buff</t>
+  </si>
+  <si>
+    <t>技能开始时的自身特效</t>
+  </si>
+  <si>
+    <t>技能命中时的目标特效</t>
+  </si>
+  <si>
+    <t>起手动画</t>
+  </si>
+  <si>
+    <t>命中动画</t>
+  </si>
+  <si>
+    <t>单个</t>
   </si>
 </sst>
 </file>
@@ -727,8 +757,12 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1051,7 +1085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
@@ -1060,11 +1094,14 @@
     <col min="4" max="4" width="18.5" style="2" customWidth="1"/>
     <col min="5" max="6" width="26.875" style="2" customWidth="1"/>
     <col min="7" max="8" width="23.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="29.375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="9" max="10" width="29.375" style="2" customWidth="1"/>
+    <col min="11" max="12" width="30.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="23.75" style="2" customWidth="1"/>
+    <col min="14" max="14" width="21" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1092,67 +1129,130 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="2:2">
+    <row r="4" s="2" customFormat="1" spans="2:11">
       <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="2">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="Cast" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -35,40 +35,52 @@
     <t>Id</t>
   </si>
   <si>
-    <t>TotalTime</t>
-  </si>
-  <si>
-    <t>SelectType</t>
-  </si>
-  <si>
-    <t>SelectParam</t>
+    <t>CastType</t>
+  </si>
+  <si>
+    <t>#Desc</t>
+  </si>
+  <si>
+    <t>*NumericTypeValue</t>
+  </si>
+  <si>
+    <t>SelfAction</t>
+  </si>
+  <si>
+    <t>SelfActionParam</t>
+  </si>
+  <si>
+    <t>SelfActionParam_Bool</t>
   </si>
   <si>
     <t>HitAction</t>
   </si>
   <si>
-    <t>HitActionTimes</t>
-  </si>
-  <si>
-    <t>SelfHitAction</t>
-  </si>
-  <si>
-    <t>SelfHitActionTimes</t>
-  </si>
-  <si>
-    <t>Buffs</t>
-  </si>
-  <si>
-    <t>StartEffect</t>
-  </si>
-  <si>
-    <t>HitEffect</t>
-  </si>
-  <si>
-    <t>StartAnimation</t>
-  </si>
-  <si>
-    <t>HitAnimation</t>
+    <t>HitActionParam</t>
+  </si>
+  <si>
+    <t>HitActionParam_Bool</t>
+  </si>
+  <si>
+    <t>FinishAction</t>
+  </si>
+  <si>
+    <t>FinishActionParam</t>
+  </si>
+  <si>
+    <t>FinishActionParam_Bool</t>
+  </si>
+  <si>
+    <t>ResName</t>
+  </si>
+  <si>
+    <t>InitCastPos_L</t>
+  </si>
+  <si>
+    <t>InitCastPos_R</t>
+  </si>
+  <si>
+    <t>InitCastScale</t>
   </si>
   <si>
     <t>##type</t>
@@ -77,52 +89,181 @@
     <t>int</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>map,ENumericType,long</t>
+  </si>
+  <si>
+    <t>(list#spe=,),int</t>
+  </si>
+  <si>
+    <t>(list#spe=,),long</t>
+  </si>
+  <si>
+    <t>(list#spe=,),bool</t>
+  </si>
+  <si>
     <t>(list#sep=,),int</t>
   </si>
   <si>
-    <t>(list#spe=,),int</t>
+    <t>(list#sep=,),long</t>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
-    <t>总时长</t>
-  </si>
-  <si>
-    <t>目标选择方式</t>
-  </si>
-  <si>
-    <t>目标选择参数</t>
+    <t>技能类型</t>
+  </si>
+  <si>
+    <t>技能描述</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>自身行为</t>
+  </si>
+  <si>
+    <t>自身行为参数</t>
   </si>
   <si>
     <t>命中行为</t>
   </si>
   <si>
-    <t>技能命中时间点</t>
-  </si>
-  <si>
-    <t>命中自身行为</t>
-  </si>
-  <si>
-    <t>技能命中自身时间点</t>
-  </si>
-  <si>
-    <t>命中Buff</t>
-  </si>
-  <si>
-    <t>技能开始时的自身特效</t>
-  </si>
-  <si>
-    <t>技能命中时的目标特效</t>
-  </si>
-  <si>
-    <t>起手动画</t>
-  </si>
-  <si>
-    <t>命中动画</t>
-  </si>
-  <si>
-    <t>单个</t>
+    <t>命中行为参数</t>
+  </si>
+  <si>
+    <t>结束行为</t>
+  </si>
+  <si>
+    <t>结束行为参数</t>
+  </si>
+  <si>
+    <t>资源名称</t>
+  </si>
+  <si>
+    <t>初始位置</t>
+  </si>
+  <si>
+    <t>初始缩放</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+  </si>
+  <si>
+    <t>枪子弹</t>
+  </si>
+  <si>
+    <t>技能物体个数_0</t>
+  </si>
+  <si>
+    <t>qiangzidan</t>
+  </si>
+  <si>
+    <t>1.2,-4.07</t>
+  </si>
+  <si>
+    <t>4.8,-4.07</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
+    <t>技能触发间隔_1</t>
+  </si>
+  <si>
+    <t>技能移动速度_1</t>
+  </si>
+  <si>
+    <t>法杖子弹</t>
+  </si>
+  <si>
+    <t>fazhangzidan</t>
+  </si>
+  <si>
+    <t>0,0</t>
+  </si>
+  <si>
+    <t>板砖</t>
+  </si>
+  <si>
+    <t>banzhuan</t>
+  </si>
+  <si>
+    <t>回旋镖</t>
+  </si>
+  <si>
+    <t>huixuanbiao</t>
+  </si>
+  <si>
+    <t>火箭</t>
+  </si>
+  <si>
+    <t>huojian</t>
+  </si>
+  <si>
+    <t>火箭爆炸</t>
+  </si>
+  <si>
+    <t>huojianboom</t>
+  </si>
+  <si>
+    <t>雷电发射器</t>
+  </si>
+  <si>
+    <t>leidian</t>
+  </si>
+  <si>
+    <t>立场发射器</t>
+  </si>
+  <si>
+    <t>lichang</t>
+  </si>
+  <si>
+    <t>榴莲</t>
+  </si>
+  <si>
+    <t>liulian</t>
+  </si>
+  <si>
+    <t>燃烧瓶</t>
+  </si>
+  <si>
+    <t>ranshaoping</t>
+  </si>
+  <si>
+    <t>燃烧瓶爆炸</t>
+  </si>
+  <si>
+    <t>ranshaopingboom</t>
+  </si>
+  <si>
+    <t>守卫者子弹</t>
+  </si>
+  <si>
+    <t>shouweizhezidan</t>
+  </si>
+  <si>
+    <t>钻头弹</t>
+  </si>
+  <si>
+    <t>zuantoudan</t>
+  </si>
+  <si>
+    <t>足球</t>
+  </si>
+  <si>
+    <t>zuqiu</t>
+  </si>
+  <si>
+    <t>鸡腿</t>
+  </si>
+  <si>
+    <t>jitui</t>
   </si>
 </sst>
 </file>
@@ -151,7 +292,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16"/>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -301,7 +443,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,6 +453,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -631,7 +779,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -655,16 +803,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -673,98 +821,113 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1085,23 +1248,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelRow="3"/>
+  <dimension ref="A1:S29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.5" style="2" customWidth="1"/>
-    <col min="5" max="6" width="26.875" style="2" customWidth="1"/>
-    <col min="7" max="8" width="23.75" style="2" customWidth="1"/>
-    <col min="9" max="10" width="29.375" style="2" customWidth="1"/>
-    <col min="11" max="12" width="30.125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="23.75" style="2" customWidth="1"/>
-    <col min="14" max="14" width="21" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="2" max="3" width="15.875" style="2" customWidth="1"/>
+    <col min="4" max="6" width="27" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="33.625" style="2" customWidth="1"/>
+    <col min="10" max="11" width="26.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="33.625" style="2" customWidth="1"/>
+    <col min="13" max="14" width="29.375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="36.625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="26.375" style="2" customWidth="1"/>
+    <col min="17" max="19" width="25.125" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,149 +1279,746 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4"/>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:14">
+        <v>26</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="2:19">
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1014</v>
+      </c>
+      <c r="H4" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1001</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="2:6">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="2:6">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="2:19">
+      <c r="B8" s="5">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="J8" s="2">
+        <v>1001</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="2:6">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="2:6">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="2:19">
+      <c r="B12" s="5">
+        <v>3</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1016</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1001</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="E13" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="E14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="6">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="2:19">
+      <c r="B16" s="5">
+        <v>4</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1016</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1001</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="E18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="6">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19">
+      <c r="B19" s="5">
+        <v>5</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1015</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1001</v>
+      </c>
+      <c r="M19" s="2">
+        <v>1013</v>
+      </c>
+      <c r="N19" s="2">
+        <v>6</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19">
+      <c r="B20" s="5">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1001</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19">
+      <c r="B21" s="5">
+        <v>7</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1017</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1001</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19">
+      <c r="B22" s="5">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1001</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19">
+      <c r="B23" s="5">
+        <v>9</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1018</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1001</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19">
+      <c r="B24" s="5">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1017</v>
+      </c>
+      <c r="H24" s="2">
         <v>20</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="2:11">
-      <c r="B4" s="3">
+      <c r="M24" s="2">
+        <v>1013</v>
+      </c>
+      <c r="N24" s="2">
+        <v>11</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19">
+      <c r="B25" s="5">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1019</v>
+      </c>
+      <c r="H25" s="2">
+        <v>4003</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1020</v>
+      </c>
+      <c r="K25" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="2">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="P25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19">
+      <c r="B26" s="5">
+        <v>12</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="2">
         <v>1001</v>
       </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>1</v>
+      <c r="P26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19">
+      <c r="B27" s="5">
+        <v>13</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1001</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19">
+      <c r="B28" s="5">
+        <v>14</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1001</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19">
+      <c r="B29" s="5">
+        <v>15</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1012</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Cast" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -44,31 +44,16 @@
     <t>*NumericTypeValue</t>
   </si>
   <si>
-    <t>SelfAction</t>
-  </si>
-  <si>
-    <t>SelfActionParam</t>
-  </si>
-  <si>
-    <t>SelfActionParam_Bool</t>
-  </si>
-  <si>
-    <t>HitAction</t>
-  </si>
-  <si>
-    <t>HitActionParam</t>
-  </si>
-  <si>
-    <t>HitActionParam_Bool</t>
-  </si>
-  <si>
-    <t>FinishAction</t>
-  </si>
-  <si>
-    <t>FinishActionParam</t>
-  </si>
-  <si>
-    <t>FinishActionParam_Bool</t>
+    <t>*SelfAction</t>
+  </si>
+  <si>
+    <t>*SelfActionParam</t>
+  </si>
+  <si>
+    <t>*HitAction</t>
+  </si>
+  <si>
+    <t>*HitActionParam</t>
   </si>
   <si>
     <t>ResName</t>
@@ -95,19 +80,10 @@
     <t>map,ENumericType,long</t>
   </si>
   <si>
-    <t>(list#spe=,),int</t>
-  </si>
-  <si>
-    <t>(list#spe=,),long</t>
-  </si>
-  <si>
-    <t>(list#spe=,),bool</t>
-  </si>
-  <si>
-    <t>(list#sep=,),int</t>
-  </si>
-  <si>
-    <t>(list#sep=,),long</t>
+    <t>list,int</t>
+  </si>
+  <si>
+    <t>list,long</t>
   </si>
   <si>
     <t>(list#sep=,),float</t>
@@ -137,12 +113,6 @@
     <t>命中行为参数</t>
   </si>
   <si>
-    <t>结束行为</t>
-  </si>
-  <si>
-    <t>结束行为参数</t>
-  </si>
-  <si>
     <t>资源名称</t>
   </si>
   <si>
@@ -161,6 +131,9 @@
     <t>技能物体个数_0</t>
   </si>
   <si>
+    <t>1001</t>
+  </si>
+  <si>
     <t>qiangzidan</t>
   </si>
   <si>
@@ -176,9 +149,18 @@
     <t>技能触发间隔_1</t>
   </si>
   <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
     <t>技能移动速度_1</t>
   </si>
   <si>
+    <t>30000</t>
+  </si>
+  <si>
     <t>法杖子弹</t>
   </si>
   <si>
@@ -191,7 +173,25 @@
     <t>板砖</t>
   </si>
   <si>
+    <t>1024</t>
+  </si>
+  <si>
     <t>banzhuan</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>技能持续时间_1</t>
+  </si>
+  <si>
+    <t>3000</t>
   </si>
   <si>
     <t>回旋镖</t>
@@ -905,28 +905,28 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1248,7 +1248,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
@@ -1256,17 +1256,13 @@
     <col min="4" max="6" width="27" style="2" customWidth="1"/>
     <col min="7" max="7" width="21.125" style="2" customWidth="1"/>
     <col min="8" max="8" width="25.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="33.625" style="2" customWidth="1"/>
-    <col min="10" max="11" width="26.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="33.625" style="2" customWidth="1"/>
-    <col min="13" max="14" width="29.375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="36.625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="26.375" style="2" customWidth="1"/>
-    <col min="17" max="19" width="25.125" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="2"/>
+    <col min="9" max="10" width="26.875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.375" style="2" customWidth="1"/>
+    <col min="12" max="14" width="25.125" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:19">
+    <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1307,148 +1303,103 @@
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:14">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:19">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:14">
+      <c r="A3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:19">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="2:19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="2:14">
       <c r="B4" s="5">
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F4" s="6">
         <v>1</v>
@@ -1459,31 +1410,35 @@
       <c r="H4" s="2">
         <v>5000</v>
       </c>
-      <c r="J4" s="2">
-        <v>1001</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="2:6">
+      <c r="I4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="2:9">
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="6">
-        <v>1000</v>
+        <v>39</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="2:6">
@@ -1491,15 +1446,15 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="6">
-        <v>10000</v>
+        <v>42</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1507,37 +1462,37 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="2:19">
+    <row r="8" s="2" customFormat="1" spans="2:14">
       <c r="B8" s="5">
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F8" s="6">
         <v>1</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="J8" s="2">
+      <c r="I8" s="2">
         <v>1001</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>47</v>
+      <c r="K8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="2:6">
@@ -1545,7 +1500,7 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F9" s="6">
         <v>1</v>
@@ -1556,7 +1511,7 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F10" s="6">
         <v>10000</v>
@@ -1564,7 +1519,7 @@
     </row>
     <row r="11" s="3" customFormat="1" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1572,445 +1527,447 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="2:19">
+    <row r="12" spans="2:14">
       <c r="B12" s="5">
         <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F12" s="6">
         <v>1</v>
       </c>
-      <c r="G12" s="2">
-        <v>1016</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1001</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6">
+      <c r="G12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="E13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="6">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="E14" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="6">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" spans="2:19">
-      <c r="B16" s="5">
+        <v>42</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:6">
+      <c r="A15" s="2"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="E15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="5">
         <v>4</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="6">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1016</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1001</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
       <c r="E17" s="6" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="F17" s="6">
         <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1016</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1001</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="E18" s="6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F18" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="E19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="6">
         <v>5000</v>
       </c>
     </row>
-    <row r="19" spans="2:19">
-      <c r="B19" s="5">
+    <row r="20" spans="2:14">
+      <c r="B20" s="5">
         <v>5</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="C20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G20" s="2">
         <v>1015</v>
       </c>
-      <c r="J19" s="2">
+      <c r="I20" s="2">
         <v>1001</v>
       </c>
-      <c r="M19" s="2">
-        <v>1013</v>
-      </c>
-      <c r="N19" s="2">
+      <c r="K20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" s="5">
         <v>6</v>
       </c>
-      <c r="P19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="2:19">
-      <c r="B20" s="5">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="C21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="J20" s="2">
+      <c r="I21" s="2">
         <v>1001</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Q20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="2:19">
-      <c r="B21" s="5">
+      <c r="L21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="5">
         <v>7</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="C22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G22" s="2">
         <v>1017</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H22" s="2">
         <v>0</v>
       </c>
-      <c r="J21" s="2">
+      <c r="I22" s="2">
         <v>1001</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="Q21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="2:19">
-      <c r="B22" s="5">
+      <c r="L22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="5">
         <v>8</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="C23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="J22" s="2">
+      <c r="I23" s="2">
         <v>1001</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="Q22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="2:19">
-      <c r="B23" s="5">
+      <c r="L23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="5">
         <v>9</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="C24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G24" s="2">
         <v>1018</v>
       </c>
-      <c r="J23" s="2">
+      <c r="I24" s="2">
         <v>1001</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="Q23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="2:19">
-      <c r="B24" s="5">
+      <c r="L24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="5">
         <v>10</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="C25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G25" s="2">
         <v>1017</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H25" s="2">
         <v>20</v>
       </c>
-      <c r="M24" s="2">
-        <v>1013</v>
-      </c>
-      <c r="N24" s="2">
+      <c r="K25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="5">
         <v>11</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="2:19">
-      <c r="B25" s="5">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="C26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G26" s="2">
         <v>1019</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H26" s="2">
         <v>4003</v>
       </c>
-      <c r="J25" s="2">
+      <c r="I26" s="2">
         <v>1020</v>
       </c>
-      <c r="K25" s="2">
+      <c r="J26" s="2">
         <v>1</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="Q25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="2:19">
-      <c r="B26" s="5">
+      <c r="L26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" s="5">
         <v>12</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="C27" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J26" s="2">
+      <c r="I27" s="2">
         <v>1001</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="Q26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="2:19">
-      <c r="B27" s="5">
+      <c r="L27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="5">
         <v>13</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="C28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="J27" s="2">
+      <c r="I28" s="2">
         <v>1001</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="K28" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="2:19">
-      <c r="B28" s="5">
+      <c r="L28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="5">
         <v>14</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="C29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J28" s="2">
+      <c r="I29" s="2">
         <v>1001</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="Q28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="2:19">
-      <c r="B29" s="5">
+      <c r="L29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="5">
         <v>15</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="C30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="J29" s="2">
+      <c r="I30" s="2">
         <v>1012</v>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="Q29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S29" s="2" t="s">
-        <v>47</v>
+      <c r="L30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2022,5 +1979,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A16:N30 I13:N13 G14:N14 A13:E14 J12:N12 A12:F12 H12 A1:F2 K1:N2 A3:N3 H5 A5:F5 A4:H4 J4:N5 A6:N11" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="Cast" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+需要先设置位置</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="83">
   <si>
     <t>##var</t>
   </si>
@@ -59,10 +91,7 @@
     <t>ResName</t>
   </si>
   <si>
-    <t>InitCastPos_L</t>
-  </si>
-  <si>
-    <t>InitCastPos_R</t>
+    <t>InitCastPos</t>
   </si>
   <si>
     <t>InitCastScale</t>
@@ -131,63 +160,72 @@
     <t>技能物体个数_0</t>
   </si>
   <si>
+    <t>1029</t>
+  </si>
+  <si>
     <t>1001</t>
   </si>
   <si>
     <t>qiangzidan</t>
   </si>
   <si>
-    <t>1.2,-4.07</t>
-  </si>
-  <si>
-    <t>4.8,-4.07</t>
+    <t>0,0</t>
+  </si>
+  <si>
+    <t>0.15,0.15</t>
+  </si>
+  <si>
+    <t>技能触发间隔_1</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>技能移动速度_1</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>法杖子弹</t>
+  </si>
+  <si>
+    <t>fazhangzidan</t>
   </si>
   <si>
     <t>1,1,1</t>
   </si>
   <si>
-    <t>技能触发间隔_1</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>技能移动速度_1</t>
-  </si>
-  <si>
-    <t>30000</t>
-  </si>
-  <si>
-    <t>法杖子弹</t>
-  </si>
-  <si>
-    <t>fazhangzidan</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
     <t>板砖</t>
   </si>
   <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>banzhuan</t>
+  </si>
+  <si>
+    <t>0.5,0.5</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
     <t>1024</t>
   </si>
   <si>
-    <t>banzhuan</t>
-  </si>
-  <si>
-    <t>1000</t>
+    <t>110000</t>
   </si>
   <si>
     <t>1025</t>
   </si>
   <si>
-    <t>10000</t>
-  </si>
-  <si>
     <t>技能持续时间_1</t>
   </si>
   <si>
@@ -200,10 +238,16 @@
     <t>huixuanbiao</t>
   </si>
   <si>
+    <t>1027</t>
+  </si>
+  <si>
     <t>火箭</t>
   </si>
   <si>
     <t>huojian</t>
+  </si>
+  <si>
+    <t>0.04,0.04</t>
   </si>
   <si>
     <t>火箭爆炸</t>
@@ -276,7 +320,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,6 +485,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1248,7 +1303,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
@@ -1258,11 +1313,11 @@
     <col min="8" max="8" width="25.75" style="2" customWidth="1"/>
     <col min="9" max="10" width="26.875" style="2" customWidth="1"/>
     <col min="11" max="11" width="26.375" style="2" customWidth="1"/>
-    <col min="12" max="14" width="25.125" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="12" max="13" width="25.125" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1300,115 +1355,103 @@
       <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:13">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="1" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:13">
+      <c r="A3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="2:14">
+    </row>
+    <row r="4" s="2" customFormat="1" spans="2:13">
       <c r="B4" s="5">
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="F4" s="6">
         <v>1</v>
       </c>
-      <c r="G4" s="2">
-        <v>1014</v>
-      </c>
-      <c r="H4" s="2">
-        <v>5000</v>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>34</v>
@@ -1421,9 +1464,6 @@
       </c>
       <c r="M4" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="2:9">
@@ -1431,12 +1471,15 @@
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
         <v>41</v>
       </c>
@@ -1454,7 +1497,7 @@
     </row>
     <row r="7" s="3" customFormat="1" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1462,23 +1505,25 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="2:14">
+    <row r="8" s="2" customFormat="1" spans="2:13">
       <c r="B8" s="5">
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" s="6">
         <v>1</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="I8" s="2">
         <v>1001</v>
       </c>
@@ -1486,13 +1531,10 @@
         <v>45</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="2:6">
@@ -1500,7 +1542,7 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="6">
         <v>1</v>
@@ -1519,7 +1561,7 @@
     </row>
     <row r="11" s="3" customFormat="1" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1527,18 +1569,18 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="2:14">
+    <row r="12" spans="2:13">
       <c r="B12" s="5">
         <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="6">
         <v>1</v>
@@ -1553,36 +1595,36 @@
         <v>49</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="E13" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="E14" s="6" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:6">
@@ -1590,64 +1632,64 @@
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="E15" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="2:14">
+    <row r="17" spans="2:13">
       <c r="B17" s="5">
         <v>4</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" s="6">
         <v>1</v>
       </c>
-      <c r="G17" s="2">
-        <v>1016</v>
+      <c r="G17" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="I17" s="2">
         <v>1001</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N17" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
+    </row>
+    <row r="18" spans="2:7">
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="E18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="6">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="2:6">
@@ -1656,318 +1698,295 @@
       <c r="E19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="6">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14">
-      <c r="B20" s="5">
+      <c r="F19" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="E20" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="5">
         <v>5</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" s="2">
+      <c r="C21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="2">
         <v>1015</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1001</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14">
-      <c r="B21" s="5">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="I21" s="2">
         <v>1001</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
       <c r="B22" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1017</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I22" s="2">
         <v>1001</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N22" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14">
+    </row>
+    <row r="23" spans="2:13">
       <c r="B23" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1017</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
       </c>
       <c r="I23" s="2">
         <v>1001</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N23" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14">
+    </row>
+    <row r="24" spans="2:13">
       <c r="B24" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1018</v>
+        <v>67</v>
       </c>
       <c r="I24" s="2">
         <v>1001</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N24" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14">
+    </row>
+    <row r="25" spans="2:13">
       <c r="B25" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2">
-        <v>1017</v>
-      </c>
-      <c r="H25" s="2">
-        <v>20</v>
+        <v>1018</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1001</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N25" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14">
+    </row>
+    <row r="26" spans="2:13">
       <c r="B26" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="H26" s="2">
-        <v>4003</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1020</v>
-      </c>
-      <c r="J26" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N26" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14">
+    </row>
+    <row r="27" spans="2:13">
       <c r="B27" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1019</v>
+      </c>
+      <c r="H27" s="2">
+        <v>4003</v>
       </c>
       <c r="I27" s="2">
-        <v>1001</v>
+        <v>1020</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14">
+    </row>
+    <row r="28" spans="2:13">
       <c r="B28" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I28" s="2">
         <v>1001</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N28" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14">
+    </row>
+    <row r="29" spans="2:13">
       <c r="B29" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I29" s="2">
         <v>1001</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N29" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14">
+    </row>
+    <row r="30" spans="2:13">
       <c r="B30" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I30" s="2">
-        <v>1012</v>
+        <v>1001</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N30" s="2" t="s">
-        <v>38</v>
+    </row>
+    <row r="31" spans="2:13">
+      <c r="B31" s="5">
+        <v>15</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I31" s="2">
+        <v>1012</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1980,7 +1999,8 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A16:N30 I13:N13 G14:N14 A13:E14 J12:N12 A12:F12 H12 A1:F2 K1:N2 A3:N3 H5 A5:F5 A4:H4 J4:N5 A6:N11" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:K4 A7:M31 G6:M6 A6:E6 A5:F5 I5:M5 M4 A1:M3" numberStoredAsText="1"/>
   </ignoredErrors>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Datas/Cast.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Cast" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="85">
   <si>
     <t>##var</t>
   </si>
@@ -172,7 +172,7 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>0.15,0.15</t>
+    <t>0.05,0.05</t>
   </si>
   <si>
     <t>技能触发间隔_1</t>
@@ -211,7 +211,7 @@
     <t>banzhuan</t>
   </si>
   <si>
-    <t>0.5,0.5</t>
+    <t>0.25,0.25</t>
   </si>
   <si>
     <t>1000</t>
@@ -238,6 +238,9 @@
     <t>huixuanbiao</t>
   </si>
   <si>
+    <t>0.3,0.3</t>
+  </si>
+  <si>
     <t>1027</t>
   </si>
   <si>
@@ -247,7 +250,7 @@
     <t>huojian</t>
   </si>
   <si>
-    <t>0.04,0.04</t>
+    <t>0.03,0.03</t>
   </si>
   <si>
     <t>火箭爆炸</t>
@@ -266,6 +269,9 @@
   </si>
   <si>
     <t>lichang</t>
+  </si>
+  <si>
+    <t>0.2,0.2</t>
   </si>
   <si>
     <t>榴莲</t>
@@ -1676,7 +1682,7 @@
         <v>36</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -1689,7 +1695,7 @@
         <v>51</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="2:6">
@@ -1720,7 +1726,7 @@
         <v>30</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G21" s="2">
         <v>1015</v>
@@ -1729,13 +1735,13 @@
         <v>1001</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="2:13">
@@ -1746,13 +1752,13 @@
         <v>30</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I22" s="2">
         <v>1001</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>36</v>
@@ -1769,7 +1775,7 @@
         <v>30</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G23" s="2">
         <v>1017</v>
@@ -1781,7 +1787,7 @@
         <v>1001</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>36</v>
@@ -1798,19 +1804,19 @@
         <v>30</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I24" s="2">
         <v>1001</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="2:13">
@@ -1821,7 +1827,7 @@
         <v>30</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2">
         <v>1018</v>
@@ -1830,13 +1836,13 @@
         <v>1001</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="2:13">
@@ -1847,7 +1853,7 @@
         <v>30</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G26" s="2">
         <v>1017</v>
@@ -1856,13 +1862,13 @@
         <v>20</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="2:13">
@@ -1873,7 +1879,7 @@
         <v>30</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G27" s="2">
         <v>1019</v>
@@ -1888,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>36</v>
@@ -1905,13 +1911,13 @@
         <v>30</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I28" s="2">
         <v>1001</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>36</v>
@@ -1928,19 +1934,19 @@
         <v>30</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I29" s="2">
         <v>1001</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="2:13">
@@ -1951,19 +1957,19 @@
         <v>30</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I30" s="2">
         <v>1001</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -1974,13 +1980,13 @@
         <v>30</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I31" s="2">
         <v>1012</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>36</v>
@@ -1999,7 +2005,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A4:K4 A7:M31 G6:M6 A6:E6 A5:F5 I5:M5 M4 A1:M3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M1 A2:K2 A3:M3 I5:M5 A5:F5 A6:E6 G6:M6 A7:M11 A12:L12 A13:M16 A17:L17 A18:M20 A21:L21 A22:M23 A24:L26 A27:M28 A29:L30 A31:M31 A4:K4" numberStoredAsText="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
